--- a/src/attributions/attributions_saliency_traj_492.xlsx
+++ b/src/attributions/attributions_saliency_traj_492.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG8"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,3984 +999,8536 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.04269816726446152</v>
+        <v>0.02958553098142147</v>
       </c>
       <c r="B2" t="n">
-        <v>2.515906095504761</v>
+        <v>0.1982782483100891</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3979654908180237</v>
+        <v>0.03628890588879585</v>
       </c>
       <c r="D2" t="n">
-        <v>0.541930079460144</v>
+        <v>0.1510592997074127</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4273510277271271</v>
+        <v>0.0744730681180954</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2565644979476929</v>
+        <v>0.0766376256942749</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2182838022708893</v>
+        <v>0.07789555191993713</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1174727752804756</v>
+        <v>0.01167590729892254</v>
       </c>
       <c r="I2" t="n">
-        <v>0.108043797314167</v>
+        <v>0.001434969250112772</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3185222744941711</v>
+        <v>0.02547949925065041</v>
       </c>
       <c r="K2" t="n">
-        <v>2.164023876190186</v>
+        <v>0.2208648025989532</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1194729134440422</v>
+        <v>0.05786796659231186</v>
       </c>
       <c r="M2" t="n">
-        <v>1.033047676086426</v>
+        <v>0.2082318663597107</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6405264735221863</v>
+        <v>0.1125391274690628</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1209872663021088</v>
+        <v>0.05090083926916122</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05728594958782196</v>
+        <v>0.03995343670248985</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2214215695858002</v>
+        <v>0.0356924869120121</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3435105681419373</v>
+        <v>0.007289819419384003</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03011757135391235</v>
+        <v>0.009375197812914848</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3601827621459961</v>
+        <v>0.03471365943551064</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05289403349161148</v>
+        <v>0.01226272899657488</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06030286848545074</v>
+        <v>0.0207213070243597</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3033559024333954</v>
+        <v>0.006289519369602203</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1806334555149078</v>
+        <v>0.01667354442179203</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09918773919343948</v>
+        <v>0.006492501124739647</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05556365847587585</v>
+        <v>0.004392710514366627</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.169604018330574</v>
+        <v>0.007394196931272745</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4304099380970001</v>
+        <v>0.02115856856107712</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3127467036247253</v>
+        <v>0.06116834655404091</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2243381440639496</v>
+        <v>0.006331637501716614</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1312603503465652</v>
+        <v>0.01141453720629215</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1387139558792114</v>
+        <v>0.07631029933691025</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.04477369040250778</v>
+        <v>0.003177614882588387</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.09042798727750778</v>
+        <v>0.02673597447574139</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.09105021506547928</v>
+        <v>0.006948448717594147</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0353698767721653</v>
+        <v>0.03591900318861008</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.1753517538309097</v>
+        <v>0.006991026923060417</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.269755482673645</v>
+        <v>0.02707492560148239</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0005396492779254913</v>
+        <v>0.02614716999232769</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.06570713222026825</v>
+        <v>0.006712948903441429</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.113156646490097</v>
+        <v>0.04163578525185585</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2686579823493958</v>
+        <v>0.03754038363695145</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.05542747676372528</v>
+        <v>0.0129327941685915</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.02631667256355286</v>
+        <v>0.01575221121311188</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0940098837018013</v>
+        <v>0.0001928725396282971</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1345456838607788</v>
+        <v>0.02163276821374893</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.236698985099792</v>
+        <v>0.1308469474315643</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1271751523017883</v>
+        <v>0.01497775502502918</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2992458641529083</v>
+        <v>0.08642122894525528</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.05648990720510483</v>
+        <v>0.0690777599811554</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.2030772864818573</v>
+        <v>0.01937081851065159</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2463937997817993</v>
+        <v>0.01196295395493507</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1703097820281982</v>
+        <v>0.01167973875999451</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.05526502802968025</v>
+        <v>0.0003894700494129211</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.2676011323928833</v>
+        <v>0.02418731525540352</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.7897961139678955</v>
+        <v>0.002360173501074314</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.4500350058078766</v>
+        <v>0.02952783927321434</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.08493249118328094</v>
+        <v>0.02753126062452793</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.260671466588974</v>
+        <v>0.01010130159556866</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.08224165439605713</v>
+        <v>0.02744128927588463</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.177574947476387</v>
+        <v>0.04813472554087639</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.01560747437179089</v>
+        <v>0.003628196194767952</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.2458833158016205</v>
+        <v>0.0149062592536211</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.2306627780199051</v>
+        <v>0.001320550218224525</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.2679229378700256</v>
+        <v>0.006808063946664333</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1109034940600395</v>
+        <v>0.0273826252669096</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.04459695518016815</v>
+        <v>0.02386283501982689</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.270796537399292</v>
+        <v>0.0343744158744812</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.04130425304174423</v>
+        <v>0.01866578124463558</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.004325328394770622</v>
+        <v>0.001970696495845914</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.005665809847414494</v>
+        <v>0.02386311255395412</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.249484047293663</v>
+        <v>0.007175149396061897</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.07387925684452057</v>
+        <v>0.009187431074678898</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.7985728979110718</v>
+        <v>0.0394948422908783</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.2753839492797852</v>
+        <v>0.000154188834130764</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.07503212988376617</v>
+        <v>0.05064208060503006</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1795317977666855</v>
+        <v>0.02052968181669712</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.005948208272457123</v>
+        <v>0.004795840475708246</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.05746493116021156</v>
+        <v>6.450462387874722e-05</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.1067995727062225</v>
+        <v>0.002652059774845839</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.08161736279726028</v>
+        <v>0.005404679104685783</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.006848059594631195</v>
+        <v>0.01315519586205482</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.3995905220508575</v>
+        <v>0.05338894575834274</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.06281844526529312</v>
+        <v>0.02466709911823273</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.1084589213132858</v>
+        <v>0.03636472299695015</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.02736931294202805</v>
+        <v>0.009564695879817009</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.02554994821548462</v>
+        <v>0.006839622743427753</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.02436637505888939</v>
+        <v>0.002992061898112297</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.05114979296922684</v>
+        <v>1.748450449667871e-05</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.005080750212073326</v>
+        <v>0.007482399698346853</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.43496173620224</v>
+        <v>0.05753660574555397</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.2858165502548218</v>
+        <v>0.03161250799894333</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.05443741381168365</v>
+        <v>0.0175044871866703</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.04839897155761719</v>
+        <v>0.007046045735478401</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.3653742074966431</v>
+        <v>0.02375924400985241</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.488705039024353</v>
+        <v>0.01751491986215115</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.2641934156417847</v>
+        <v>0.01366249565035105</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.272756040096283</v>
+        <v>0.03314585611224174</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.1328884214162827</v>
+        <v>0.01109533477574587</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0003180857747793198</v>
+        <v>0.01517429109662771</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.4215240478515625</v>
+        <v>0.05566353350877762</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.1399198770523071</v>
+        <v>0.01498794555664062</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.1184025034308434</v>
+        <v>0.03573548048734665</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.007098070345818996</v>
+        <v>0.01458263490349054</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.006586428266018629</v>
+        <v>0.01096152421087027</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.01910472474992275</v>
+        <v>0.004377301782369614</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.007672920823097229</v>
+        <v>0.005702982656657696</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.003755934536457062</v>
+        <v>0.008252513594925404</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.02454130165278912</v>
+        <v>0.05077359080314636</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.6454647779464722</v>
+        <v>0.08266645669937134</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.2337465584278107</v>
+        <v>0.05406160652637482</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.332338273525238</v>
+        <v>0.05207085609436035</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.2950915992259979</v>
+        <v>0.09019546955823898</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.2526943683624268</v>
+        <v>0.04773341491818428</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.2172446399927139</v>
+        <v>0.02258174307644367</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.1493087261915207</v>
+        <v>0.04357561841607094</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.05628378689289093</v>
+        <v>0.02091063000261784</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.04241218417882919</v>
+        <v>0.003890265710651875</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.5192721486091614</v>
+        <v>0.0513969399034977</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.2275807559490204</v>
+        <v>0.01425483636558056</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.05599242076277733</v>
+        <v>0.02389022707939148</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.3100385069847107</v>
+        <v>0.02415887452661991</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.04082939028739929</v>
+        <v>0.05927253141999245</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.01050202175974846</v>
+        <v>0.004240844398736954</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0157031174749136</v>
+        <v>0.001733238226734102</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.02430951222777367</v>
+        <v>0.02553372457623482</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.1394340693950653</v>
+        <v>0.03241880238056183</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2777102589607239</v>
+        <v>0.005640391260385513</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.1479381918907166</v>
+        <v>0.001399367582052946</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.1857645809650421</v>
+        <v>0.001504922285676003</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.1604270339012146</v>
+        <v>0.004269968718290329</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.3511962592601776</v>
+        <v>0.01736226677894592</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.009925516322255135</v>
+        <v>0.002288180636242032</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.1766092032194138</v>
+        <v>0.0315105989575386</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.004245268180966377</v>
+        <v>0.04276250302791595</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.00437898188829422</v>
+        <v>0.01214918959885836</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.2674691677093506</v>
+        <v>0.06427545100450516</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.12629035115242</v>
+        <v>0.01211261842399836</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.04016518220305443</v>
+        <v>0.026419997215271</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.238278403878212</v>
+        <v>0.02247997932136059</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0536344088613987</v>
+        <v>0.02985681407153606</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.04579168185591698</v>
+        <v>0.008559279143810272</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0006650537252426147</v>
+        <v>0.0017137979157269</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.058870829641819</v>
+        <v>0.006707526743412018</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.004570461809635162</v>
+        <v>0.01961538381874561</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.1723159104585648</v>
+        <v>0.006126869469881058</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.3194759786128998</v>
+        <v>0.01385479979217052</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.1273189783096313</v>
+        <v>0.01971417292952538</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.1899912059307098</v>
+        <v>0.0004701705183833838</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.08374738693237305</v>
+        <v>0.02821355871856213</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.007320813834667206</v>
+        <v>0.01431409176439047</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0954991951584816</v>
+        <v>0.001173097640275955</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.04560217261314392</v>
+        <v>0.02224777452647686</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.02964567393064499</v>
+        <v>0.01510787196457386</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.413950115442276</v>
+        <v>0.06732187420129776</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.07750125229358673</v>
+        <v>0.01277866773307323</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.109843336045742</v>
+        <v>0.03824954107403755</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.03510507568717003</v>
+        <v>0.007490378338843584</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0005199583247303963</v>
+        <v>0.007787127979099751</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.02260207012295723</v>
+        <v>0.009541730396449566</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.004214722663164139</v>
+        <v>0.006315121427178383</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.001267664134502411</v>
+        <v>0.001962572569027543</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.08183483779430389</v>
+        <v>0.01468882244080305</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.005677737295627594</v>
+        <v>0.03245642781257629</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.009836466051638126</v>
+        <v>0.02629888616502285</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.02660128474235535</v>
+        <v>0.03566741198301315</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.1532959342002869</v>
+        <v>0.002192178275436163</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.1819475591182709</v>
+        <v>0.01379465870559216</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.07018818706274033</v>
+        <v>0.003324456047266722</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.1461204439401627</v>
+        <v>0.001366802956908941</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.09346725791692734</v>
+        <v>0.03590643405914307</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.03532358631491661</v>
+        <v>0.009988926351070404</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.3061084747314453</v>
+        <v>0.06079529970884323</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.04021895676851273</v>
+        <v>0.01930707693099976</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.421185314655304</v>
+        <v>0.09884440153837204</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.04981512948870659</v>
+        <v>0.09417091310024261</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.1455209255218506</v>
+        <v>0.04410713538527489</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.2023098319768906</v>
+        <v>0.01949390396475792</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.04734698683023453</v>
+        <v>0.00806278083473444</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.009727765806019306</v>
+        <v>0.01548437867313623</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.118356391787529</v>
+        <v>0.02299175411462784</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.1304690688848495</v>
+        <v>0.03797918558120728</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.1961072832345963</v>
+        <v>0.007539810612797737</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.026154525578022</v>
+        <v>0.02298282831907272</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.4381886720657349</v>
+        <v>0.07908996939659119</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.2135970443487167</v>
+        <v>0.004308779258280993</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.2705681324005127</v>
+        <v>0.04694458097219467</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.0325234979391098</v>
+        <v>0.02628661133348942</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.04079997166991234</v>
+        <v>0.01358984410762787</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.2565650343894958</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.3915290832519531</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.0742974728345871</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.2459885776042938</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.05585974454879761</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.05868135020136833</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.1014563739299774</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.0669783353805542</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.9839636087417603</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.08815935254096985</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.6475790143013</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.07478553056716919</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.2504268884658813</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.1616513133049011</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.02743862569332123</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1812224239110947</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.2381385117769241</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.8223363161087036</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.07890696823596954</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.1368251740932465</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.03953694552183151</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3152200281620026</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5040667653083801</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.1937911808490753</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.1747307479381561</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.06139592081308365</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.3176453113555908</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.06332054734230042</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.17869533598423</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.1398758888244629</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.3282823264598846</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.0775093138217926</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.2507385909557343</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.03928098082542419</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.4646504819393158</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.2464369535446167</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.04147268459200859</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.04374376311898232</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.1817721277475357</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.04456876963376999</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.1940881907939911</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.1193862929940224</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.0514172837138176</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.2164770215749741</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.1262953281402588</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.09822910279035568</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.5332082509994507</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.1055408120155334</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.01698830723762512</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.03878699615597725</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.1513713747262955</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.1716067045927048</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.06393669545650482</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.4818410575389862</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.1225465312600136</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.08453197777271271</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>0.07015544176101685</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.384204089641571</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.305932492017746</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.1640790700912476</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.1300933957099915</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.5417593717575073</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.1900528967380524</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.2083885967731476</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.3076827228069305</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.06301466375589371</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.04557482898235321</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.2776122987270355</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.02827285975217819</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>0.1042589396238327</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.2760435938835144</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.2449683099985123</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.01824039965867996</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.1006100028753281</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.1518453359603882</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.2821226418018341</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.3596003353595734</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>0.1603375375270844</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.174195259809494</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.199251189827919</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.5882459878921509</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.04534757882356644</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.02978717535734177</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.0002858070656657219</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.102022759616375</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.01200767420232296</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>0.0111916558817029</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.007330875843763351</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>0.04014180228114128</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.2159706354141235</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.09596151113510132</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.3778972923755646</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.1373368501663208</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.1251504123210907</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.4023070633411407</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.3960450887680054</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.04033057391643524</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.2608366906642914</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.2272373139858246</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.03069299086928368</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.0466616079211235</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.02122354879975319</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.0601908266544342</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.06800952553749084</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>0.07238467037677765</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.01227761805057526</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>0.02676707692444324</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.2214891910552979</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.02307774126529694</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.5163606405258179</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.03073040768504143</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.3682593703269958</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.6196891069412231</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.108526237308979</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.2977818250656128</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.2242748886346817</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.2472469210624695</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.01464940793812275</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.1316717565059662</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.1959332823753357</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.03241495788097382</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.09341014921665192</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.09887290000915527</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.3334601521492004</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.03722615540027618</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.07975998520851135</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.01440973579883575</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.2466375231742859</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.1983316540718079</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>0.03995995223522186</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.2458837330341339</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.07865138351917267</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.1840032935142517</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.04999731481075287</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>5.49759715795517e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.195011779665947</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.08224742114543915</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.01647553779184818</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.1346820443868637</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>0.04112207517027855</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>0.01712881401181221</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.05680176988244057</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.09360727667808533</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>0.2223417162895203</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.06656613945960999</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>0.3001970648765564</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.01442177034914494</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.1339598149061203</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.04604032263159752</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.05859201028943062</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.02982191741466522</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>0.1234823763370514</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.1277307868003845</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.06663145869970322</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.1018241122364998</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>0.02327926456928253</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.03583280369639397</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.03632290288805962</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.03062578663229942</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.02144471555948257</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.04279840737581253</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.2487253546714783</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.1026540771126747</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.1496545672416687</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.0758584663271904</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.2161825448274612</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.01359526999294758</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.03179179504513741</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.3907395005226135</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.07853735983371735</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.2059856355190277</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.01201988011598587</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.1658577620983124</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.234473317861557</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.2304813712835312</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.707628607749939</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.02937142550945282</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.06844539940357208</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.1772906184196472</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.2894445061683655</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.07248575985431671</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.1114665120840073</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.06711027026176453</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.1725510805845261</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.01680266857147217</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.06697040796279907</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.08792123943567276</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.283625066280365</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>0.3462989628314972</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>0.09412272274494171</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.4165091812610626</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.2076653689146042</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.2097081542015076</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.144483357667923</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.490388423204422</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.04767275601625443</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.1595956981182098</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.1308704316616058</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.06424439698457718</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.4992785453796387</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.2632622122764587</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.2664874792098999</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.03346493095159531</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.4242269396781921</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.003377074375748634</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.1309739351272583</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.1324716508388519</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.002909474540501833</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.05918190628290176</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.02564694546163082</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1344013065099716</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.107310526072979</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.0106654642149806</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.04077819362282753</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>0.01702767238020897</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>0.05774617940187454</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.03537536412477493</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>0.01042154058814049</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>0.07517984509468079</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.2896008789539337</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.04791007936000824</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>0.07169827818870544</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>0.1043163388967514</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>0.1647521257400513</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>0.01414071675390005</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>0.04022900760173798</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.09103885293006897</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>0.0004968345165252686</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>0.1057742610573769</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>0.04796626791357994</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>0.03863735869526863</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.01831471361219883</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>0.07425981760025024</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>0.06470756232738495</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>0.05846540629863739</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>0.4723455011844635</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>0.06965886801481247</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>0.1284415572881699</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>0.01912510022521019</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>0.2035782784223557</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>0.08386795222759247</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>0.000904299202375114</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>0.006407281849533319</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>0.04067811742424965</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>0.05396942794322968</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>0.1040353924036026</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>0.1537995785474777</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>0.0003297170624136925</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>0.1918976753950119</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>0.03441741317510605</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>0.04917654767632484</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>0.1565718203783035</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>0.04517477005720139</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>0.03485026955604553</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>0.05875248461961746</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>0.03587988018989563</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>0.07210647314786911</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>0.06874353438615799</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>0.1885594576597214</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>0.004450741223990917</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>0.07370726019144058</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>0.02965212985873222</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>0.2066270411014557</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>0.005309328902512789</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>0.1006227508187294</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>0.02588034607470036</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>0.1839956343173981</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>0.03486040979623795</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>0.02711443975567818</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>0.1040989831089973</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>0.006223858334124088</v>
       </c>
       <c r="CE4" t="n">
-        <v>0</v>
+        <v>0.1200558245182037</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>0.06603466719388962</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>0.04866522550582886</v>
       </c>
       <c r="CH4" t="n">
-        <v>0</v>
+        <v>0.02728402242064476</v>
       </c>
       <c r="CI4" t="n">
-        <v>0</v>
+        <v>0.1182973682880402</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>0.04592242836952209</v>
       </c>
       <c r="CK4" t="n">
-        <v>0</v>
+        <v>0.03721176832914352</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>0.01439111307263374</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>0.01188127882778645</v>
       </c>
       <c r="CN4" t="n">
-        <v>0</v>
+        <v>0.1290452629327774</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>0.0658121258020401</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>0.00660686194896698</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0</v>
+        <v>0.03869497776031494</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>0.148414209485054</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>0.1000490263104439</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>0.02905235812067986</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>0.07414532452821732</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>0.01578242145478725</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>0.1170292794704437</v>
       </c>
       <c r="CX4" t="n">
-        <v>0</v>
+        <v>0.0760260745882988</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>0.04595047235488892</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0</v>
+        <v>0.02372205816209316</v>
       </c>
       <c r="DA4" t="n">
-        <v>0</v>
+        <v>0.1312927305698395</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>0.03106986731290817</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>0.04127261787652969</v>
       </c>
       <c r="DD4" t="n">
-        <v>0</v>
+        <v>0.01487555541098118</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>0.08440034091472626</v>
       </c>
       <c r="DF4" t="n">
-        <v>0</v>
+        <v>0.09196072816848755</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>0.01805419847369194</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>0.02971192821860313</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>0.05762335285544395</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>0.2337071448564529</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>0.008969089016318321</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>0.05270189791917801</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>0.006429105997085571</v>
       </c>
       <c r="DN4" t="n">
-        <v>0</v>
+        <v>0.02366150543093681</v>
       </c>
       <c r="DO4" t="n">
-        <v>0</v>
+        <v>0.07868083566427231</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>0.09800893068313599</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0</v>
+        <v>0.06770246475934982</v>
       </c>
       <c r="DR4" t="n">
-        <v>0</v>
+        <v>0.0902726873755455</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>0.08676884323358536</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>0.02691604569554329</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>0.003931914456188679</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>0.01328836195170879</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>0.007391229271888733</v>
       </c>
       <c r="DX4" t="n">
-        <v>0</v>
+        <v>0.03738172724843025</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>0.07873454689979553</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>0.07341869175434113</v>
       </c>
       <c r="EA4" t="n">
-        <v>0</v>
+        <v>0.04195031523704529</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>0.1162545382976532</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>0.07633265852928162</v>
       </c>
       <c r="ED4" t="n">
-        <v>0</v>
+        <v>0.08135397732257843</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>0.08760305494070053</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>0.006060893647372723</v>
       </c>
       <c r="EG4" t="n">
-        <v>0</v>
+        <v>0.0492933914065361</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>0.01925814338028431</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>0.0653376579284668</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0</v>
+        <v>0.04844798892736435</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>0.07131358236074448</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>0.01407319772988558</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>0.01482318993657827</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>0.04458217322826385</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>0.01269328780472279</v>
       </c>
       <c r="EP4" t="n">
-        <v>0</v>
+        <v>0.009881231933832169</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>0.05619218572974205</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>0.04767049103975296</v>
       </c>
       <c r="ES4" t="n">
-        <v>0</v>
+        <v>0.07450892776250839</v>
       </c>
       <c r="ET4" t="n">
-        <v>0</v>
+        <v>0.07092170417308807</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>0.08047419041395187</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>0.006666983477771282</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>0.02048283070325851</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>0.0001979107037186623</v>
       </c>
       <c r="EY4" t="n">
-        <v>0</v>
+        <v>0.1393394768238068</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>0.05431869998574257</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>0.04416761547327042</v>
       </c>
       <c r="FB4" t="n">
-        <v>0</v>
+        <v>0.05715526267886162</v>
       </c>
       <c r="FC4" t="n">
-        <v>0</v>
+        <v>0.109879195690155</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>0.03481853008270264</v>
       </c>
       <c r="FE4" t="n">
-        <v>0</v>
+        <v>0.03235293924808502</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>0.01219552848488092</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>0.0001228079199790955</v>
       </c>
       <c r="FH4" t="n">
-        <v>0</v>
+        <v>0.1252054423093796</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>0.04915439337491989</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0</v>
+        <v>0.01054711826145649</v>
       </c>
       <c r="FK4" t="n">
-        <v>0</v>
+        <v>0.08871844410896301</v>
       </c>
       <c r="FL4" t="n">
-        <v>0</v>
+        <v>0.02112904749810696</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>0.06336142867803574</v>
       </c>
       <c r="FN4" t="n">
-        <v>0</v>
+        <v>0.02258088812232018</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>0.07204098999500275</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>0.06777507811784744</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0</v>
+        <v>0.1769995540380478</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>0.0042094886302948</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>0.1380661427974701</v>
       </c>
       <c r="FT4" t="n">
-        <v>0</v>
+        <v>0.1381608992815018</v>
       </c>
       <c r="FU4" t="n">
-        <v>0</v>
+        <v>0.03070415183901787</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>0.0516730472445488</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>0.01962290331721306</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>0.09561942517757416</v>
       </c>
       <c r="FY4" t="n">
-        <v>0</v>
+        <v>0.1200697869062424</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0</v>
+        <v>0.04529641941189766</v>
       </c>
       <c r="GA4" t="n">
-        <v>0</v>
+        <v>0.2033338844776154</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>0.1113739237189293</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>0.1242430955171585</v>
       </c>
       <c r="GD4" t="n">
-        <v>0</v>
+        <v>0.11408631503582</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>0.01517602987587452</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>0.05383793264627457</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>0.04373427852988243</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>0.03640676289796829</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.2299049496650696</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.05277940258383751</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.1856000423431396</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.1341300457715988</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.02895956486463547</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.05693753063678741</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.01218504551798105</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.009673824533820152</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.07932562381029129</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.274063378572464</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.07165037840604782</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.2311335504055023</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.1582799106836319</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.02054184302687645</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.01499699242413044</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.05114630609750748</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.01711983233690262</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.001347543206065893</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0346670001745224</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.00252533657476306</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.01694044284522533</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.009481247514486313</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.02811585552990437</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.01166594214737415</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>0.003677725326269865</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.01686755008995533</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.029735017567873</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.1024724394083023</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>0.02808988094329834</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.003131435252726078</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.07443402707576752</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.01736548729240894</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>0.02534597553312778</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>0.03082846850156784</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>0.02658884413540363</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.01142039336264133</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.03937742859125137</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.05163301154971123</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>0.0001944471150636673</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>0.01619376800954342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>0.03247202187776566</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.01537648774683475</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.01516722794622183</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>0.01170467026531696</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>0.01178680919110775</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>0.1516350507736206</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.03425901010632515</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.0633026659488678</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>0.07064440101385117</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>0.005264516919851303</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>0.02386016026139259</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>0.003748830407857895</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>0.002688200213015079</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>0.06629408895969391</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>0.00442781113088131</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>0.04974165186285973</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>0.01896467432379723</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>0.03110175579786301</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>0.001365967444144189</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>0.03239291161298752</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>0.0085722915828228</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>0.01197798270732164</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>0.0003822818398475647</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>0.001323262229561806</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>0.02053931355476379</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>0.04793410748243332</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>0.06902727484703064</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>0.01649477332830429</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>0.008098792284727097</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>0.02215967886149883</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>0.004131173249334097</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>0.008705839514732361</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>0.05394353345036507</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>0.006898657418787479</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>0.02575873397290707</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>0.0192745216190815</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>0.01823508739471436</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>0.01339572761207819</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>0.004429090768098831</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>0.003814460476860404</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>0.01507743261754513</v>
       </c>
       <c r="CE5" t="n">
-        <v>0</v>
+        <v>0.06287304311990738</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>0.01898626238107681</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>0.03527570515871048</v>
       </c>
       <c r="CH5" t="n">
-        <v>0</v>
+        <v>0.01824314147233963</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>0.009617536328732967</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>0.006074646953493357</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>0.006648743990808725</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>0.004494020249694586</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>0.06292513012886047</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>0.06143151223659515</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>0.007555049378424883</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>0.03289918974041939</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0</v>
+        <v>0.03382579609751701</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>0.004846942611038685</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>0.0238064955919981</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>0.03025519102811813</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>0.01089879777282476</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>0.02012606337666512</v>
       </c>
       <c r="CW5" t="n">
-        <v>0</v>
+        <v>0.06212460249662399</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>0.006368394941091537</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>0.03342922776937485</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>0.02388970926403999</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>0.01574660837650299</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>0.008552828803658485</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>0.0009655265603214502</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>0.009298030287027359</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>0.04172701388597488</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>0.04191139712929726</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>0.09260790050029755</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>0.01361263170838356</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>0.100793868303299</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>0.03993979468941689</v>
       </c>
       <c r="DK5" t="n">
-        <v>0</v>
+        <v>0.03533940017223358</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>0.04527627304196358</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>0.03614763170480728</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>0.009714888408780098</v>
       </c>
       <c r="DO5" t="n">
-        <v>0</v>
+        <v>0.04841188713908195</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>0.03855471685528755</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>0.05437188595533371</v>
       </c>
       <c r="DR5" t="n">
-        <v>0</v>
+        <v>0.04607076570391655</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.06295359134674072</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>0.01348552946001291</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>0.002334240591153502</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>0.02679735980927944</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.04076070338487625</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>0.03493499755859375</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>0.01649171486496925</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>0.02321989275515079</v>
       </c>
       <c r="EA5" t="n">
-        <v>0</v>
+        <v>0.006235407665371895</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>0.02502246759831905</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>0.01301876083016396</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>0.032565638422966</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>0.02956333197653294</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>0.01582820899784565</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>0.07060535252094269</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>0.02447254583239555</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>0.04292657598853111</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0</v>
+        <v>0.03861046954989433</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>0.02891741879284382</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>0.00650085462257266</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>0.002649320056661963</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>0.000780681730248034</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>0.01370946690440178</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>0.01186104025691748</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>0.007102797273546457</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>0.0003914590924978256</v>
       </c>
       <c r="ES5" t="n">
-        <v>0</v>
+        <v>0.04282960668206215</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>0.0465155765414238</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>0.00792902335524559</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>0.001028749858960509</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>0.02453848347067833</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>0.0138401947915554</v>
       </c>
       <c r="EY5" t="n">
-        <v>0</v>
+        <v>0.07427918165922165</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>0.002850816119462252</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>0.03549841046333313</v>
       </c>
       <c r="FB5" t="n">
-        <v>0</v>
+        <v>0.0167695265263319</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>0.007290036417543888</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>0.01366431266069412</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>0.002681178506463766</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>0.0006943776388652623</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>0.01620642468333244</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>0.02156523242592812</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>0.02509894222021103</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>0.01719131320714951</v>
       </c>
       <c r="FK5" t="n">
-        <v>0</v>
+        <v>0.01248315256088972</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>0.005412894301116467</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>0.008497186005115509</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>0.01774684153497219</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>0.04554563388228416</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>0.01173859834671021</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>0.09774781763553619</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>0.03301855176687241</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>0.07127377390861511</v>
       </c>
       <c r="FT5" t="n">
-        <v>0</v>
+        <v>0.1066551133990288</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>0.03799921646714211</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>0.03339290246367455</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>0.04760293662548065</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>0.03903437033295631</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>0.007472043856978416</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>0.05059503018856049</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>0.04803542792797089</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>0.01817991770803928</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>0.1093530729413033</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>0.03029299527406693</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>0.05112855136394501</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>0.01941129751503468</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>0.01259423885494471</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.01613206788897514</v>
+        <v>0.2045188099145889</v>
       </c>
       <c r="B6" t="n">
-        <v>0.007665522396564484</v>
+        <v>0.6062361001968384</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03150459006428719</v>
+        <v>0.5132924318313599</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0158160924911499</v>
+        <v>0.08348001539707184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06556129455566406</v>
+        <v>0.1617376655340195</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2741329371929169</v>
+        <v>1.148956298828125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0497051477432251</v>
+        <v>0.1110600680112839</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07359324395656586</v>
+        <v>0.2820022702217102</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006652170792222023</v>
+        <v>0.03320792689919472</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00263298861682415</v>
+        <v>0.2075826674699783</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03220851719379425</v>
+        <v>0.7004761695861816</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008745503146201372</v>
+        <v>0.6393420696258545</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05281488597393036</v>
+        <v>0.02083473652601242</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09912106394767761</v>
+        <v>0.3162850141525269</v>
       </c>
       <c r="O6" t="n">
-        <v>0.22998046875</v>
+        <v>1.019722104072571</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01834109984338284</v>
+        <v>0.02233459427952766</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1032773330807686</v>
+        <v>0.4752568900585175</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003826148342341185</v>
+        <v>0.154257133603096</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003525172360241413</v>
+        <v>0.1623075902462006</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04771983250975609</v>
+        <v>0.003988062962889671</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03240410983562469</v>
+        <v>0.06867280602455139</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008350549265742302</v>
+        <v>0.04864033311605453</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02369037643074989</v>
+        <v>0.1036390289664268</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04857383668422699</v>
+        <v>0.3056071996688843</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02803274057805538</v>
+        <v>0.04482103511691093</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04834592714905739</v>
+        <v>0.05500485748052597</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02115712501108646</v>
+        <v>0.0215168409049511</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02726161479949951</v>
+        <v>0.1282322257757187</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.002612264361232519</v>
+        <v>0.1177269816398621</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.02829195931553841</v>
+        <v>0.1778698861598969</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.007390547543764114</v>
+        <v>0.2897400856018066</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.06257691234350204</v>
+        <v>0.06114767491817474</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.007617512717843056</v>
+        <v>0.2798754870891571</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.009452087804675102</v>
+        <v>0.03813183307647705</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0119242575019598</v>
+        <v>0.2291139215230942</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01953870430588722</v>
+        <v>0.2993592917919159</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02625119127333164</v>
+        <v>0.2304135411977768</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.006723690778017044</v>
+        <v>0.2707392275333405</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.005148118827491999</v>
+        <v>0.04789911210536957</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.00169716402888298</v>
+        <v>0.09840285778045654</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.004478262737393379</v>
+        <v>0.2916391491889954</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.05154316127300262</v>
+        <v>0.1824055463075638</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01103415619581938</v>
+        <v>0.0390278659760952</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.05035162717103958</v>
+        <v>0.09961605072021484</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.04474189504981041</v>
+        <v>0.1230454742908478</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.01851240545511246</v>
+        <v>0.1152421683073044</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03318368270993233</v>
+        <v>0.6509785056114197</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.01788722351193428</v>
+        <v>0.1283378303050995</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1012110710144043</v>
+        <v>0.06559590250253677</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1234514117240906</v>
+        <v>0.04147125780582428</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1561572551727295</v>
+        <v>0.9123360514640808</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.02195869386196136</v>
+        <v>0.3242632150650024</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.06561017036437988</v>
+        <v>0.2431397438049316</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.05012873932719231</v>
+        <v>0.1137418672442436</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.02250471711158752</v>
+        <v>0.009130247868597507</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0295080877840519</v>
+        <v>0.4947656095027924</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0217570997774601</v>
+        <v>0.396750420331955</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0003168843686580658</v>
+        <v>0.2928767800331116</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01219259202480316</v>
+        <v>0.06128641217947006</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0504593625664711</v>
+        <v>0.01548559032380581</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.01649578846991062</v>
+        <v>0.2682468593120575</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.06031569838523865</v>
+        <v>0.01638937182724476</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.05716298148036003</v>
+        <v>0.1060766279697418</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.02664505504071712</v>
+        <v>0.08033982664346695</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.05885028094053268</v>
+        <v>0.0300341434776783</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.06129314377903938</v>
+        <v>0.02459843829274178</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.06243465840816498</v>
+        <v>0.1718635857105255</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.05056614056229591</v>
+        <v>0.05540303140878677</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01445685792714357</v>
+        <v>0.06319361180067062</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.004578745923936367</v>
+        <v>0.03208168223500252</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.03317228332161903</v>
+        <v>0.172327920794487</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.02660082280635834</v>
+        <v>0.1428442895412445</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.01216806098818779</v>
+        <v>0.1670383363962173</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.06173479184508324</v>
+        <v>0.3078130483627319</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.001567542552947998</v>
+        <v>0.120209313929081</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.05817551910877228</v>
+        <v>0.2138576060533524</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.03811520710587502</v>
+        <v>0.01744602993130684</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.07289502024650574</v>
+        <v>0.7338546514511108</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.02204104699194431</v>
+        <v>0.1943709403276443</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.01506533194333315</v>
+        <v>0.0926859974861145</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.01156461983919144</v>
+        <v>0.06859029829502106</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.007022015750408173</v>
+        <v>0.0326015017926693</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.02437042817473412</v>
+        <v>0.2508121728897095</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.00269832881167531</v>
+        <v>0.06880186498165131</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.02157002314925194</v>
+        <v>0.03794191405177116</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.00836388673633337</v>
+        <v>0.06571832299232483</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.04901221394538879</v>
+        <v>0.2659934759140015</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.004623271524906158</v>
+        <v>0.01651925593614578</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.02130213379859924</v>
+        <v>0.07228202372789383</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.005765557754784822</v>
+        <v>0.03586238622665405</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.003888285718858242</v>
+        <v>0.3594151735305786</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.007271134294569492</v>
+        <v>0.03495316952466965</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.02970239520072937</v>
+        <v>0.2661991119384766</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.06433458626270294</v>
+        <v>0.3480065166950226</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.06991110742092133</v>
+        <v>0.2400934100151062</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0003622365184128284</v>
+        <v>0.3723009824752808</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.02511529251933098</v>
+        <v>0.1790837943553925</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.01425100117921829</v>
+        <v>0.1800837367773056</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.004399845376610756</v>
+        <v>0.1525919586420059</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.006894976831972599</v>
+        <v>0.07237889617681503</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.01542935147881508</v>
+        <v>0.2789367735385895</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.01464061345905066</v>
+        <v>0.1133785545825958</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.01953358948230743</v>
+        <v>0.02989548072218895</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.006807542406022549</v>
+        <v>0.07000645250082016</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.05013242736458778</v>
+        <v>0.2962036430835724</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.001269248314201832</v>
+        <v>0.007333843968808651</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.02886177971959114</v>
+        <v>0.04874811321496964</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.01451333239674568</v>
+        <v>0.01408791169524193</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.05217323824763298</v>
+        <v>0.1230708137154579</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0606423132121563</v>
+        <v>0.1797378957271576</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.04100581258535385</v>
+        <v>0.1343548893928528</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.09056849777698517</v>
+        <v>0.07021723687648773</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07083965092897415</v>
+        <v>0.2412630021572113</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.006811744999140501</v>
+        <v>0.5030133724212646</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.03788888826966286</v>
+        <v>0.1007736772298813</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.06733708828687668</v>
+        <v>0.277281254529953</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.02207598090171814</v>
+        <v>0.03741420432925224</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.01840979047119617</v>
+        <v>0.09364891052246094</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.02489075064659119</v>
+        <v>0.09960904717445374</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.003292246023193002</v>
+        <v>0.1144181713461876</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.02050979994237423</v>
+        <v>0.06041182950139046</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0006741322576999664</v>
+        <v>0.1739019453525543</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.01435558032244444</v>
+        <v>0.05394193902611732</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.01929777860641479</v>
+        <v>0.0307029727846384</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.02396548166871071</v>
+        <v>0.247835785150528</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.01368667930364609</v>
+        <v>0.0141203235834837</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.01256462931632996</v>
+        <v>0.06498504430055618</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.03085131756961346</v>
+        <v>0.2525280714035034</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.04139460623264313</v>
+        <v>0.147893950343132</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0244116485118866</v>
+        <v>0.07882897555828094</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.09121258556842804</v>
+        <v>0.119930662214756</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.009922608733177185</v>
+        <v>0.2708944380283356</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.006484606768935919</v>
+        <v>0.0690300464630127</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.007363269571214914</v>
+        <v>0.2379822432994843</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.03708159178495407</v>
+        <v>0.140027642250061</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0273514986038208</v>
+        <v>0.0816233903169632</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.01643993332982063</v>
+        <v>0.2139773070812225</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.02074568532407284</v>
+        <v>0.001964390277862549</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.08749523758888245</v>
+        <v>0.03973682597279549</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0003027897328138351</v>
+        <v>0.0292877908796072</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.07188853621482849</v>
+        <v>0.07585977017879486</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.005964882671833038</v>
+        <v>0.05049597471952438</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.02340072952210903</v>
+        <v>0.0436813160777092</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.008462224155664444</v>
+        <v>0.01519451010972261</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.006909595802426338</v>
+        <v>0.03858514875173569</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.07699127495288849</v>
+        <v>0.03162509202957153</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01749864965677261</v>
+        <v>0.01485400646924973</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.08055879175662994</v>
+        <v>0.1288900822401047</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.05819140747189522</v>
+        <v>0.05971398949623108</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.01412083953619003</v>
+        <v>0.1444050669670105</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.004802949260920286</v>
+        <v>0.05047254264354706</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.05082898959517479</v>
+        <v>0.01653622463345528</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.01507120113819838</v>
+        <v>0.2047491073608398</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.01097294874489307</v>
+        <v>0.03929328173398972</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.02564012631773949</v>
+        <v>0.279400110244751</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.02615288645029068</v>
+        <v>0.1002985611557961</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.02116524800658226</v>
+        <v>0.013727817684412</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0148473959416151</v>
+        <v>0.01776347681879997</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.04754520952701569</v>
+        <v>0.3072007298469543</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.008086490444839001</v>
+        <v>0.01131062768399715</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.02762933447957039</v>
+        <v>0.08401328325271606</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.02053796872496605</v>
+        <v>0.04252104461193085</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.01302130334079266</v>
+        <v>0.02539485320448875</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.01872623525559902</v>
+        <v>0.2049848139286041</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.004779875744134188</v>
+        <v>0.08209870755672455</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.02373175881803036</v>
+        <v>0.06237636506557465</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.06796170771121979</v>
+        <v>0.1135639920830727</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.07342612743377686</v>
+        <v>0.2379304468631744</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0009032660163938999</v>
+        <v>0.01568426191806793</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.02397754415869713</v>
+        <v>0.2160920798778534</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.01786112412810326</v>
+        <v>0.2614018619060516</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.03815293684601784</v>
+        <v>0.09389862418174744</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.002481258474290371</v>
+        <v>0.1060884743928909</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.01217154134064913</v>
+        <v>0.2350565493106842</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.01163177005946636</v>
+        <v>0.3244948387145996</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.1101320385932922</v>
+        <v>0.2637920677661896</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.04051318019628525</v>
+        <v>0.3118112087249756</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.01172935590147972</v>
+        <v>0.3785092830657959</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.04544179886579514</v>
+        <v>0.2313345670700073</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0006481220480054617</v>
+        <v>0.2708038687705994</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.01221228670328856</v>
+        <v>0.1253350973129272</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.004520545713603497</v>
+        <v>0.1515633463859558</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0005953984800726175</v>
+        <v>0.1567124426364899</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.01283349562436342</v>
+        <v>0.1031753420829773</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.07864842563867569</v>
+        <v>0.2852566838264465</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0103849284350872</v>
+        <v>0.2732920944690704</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.009321052581071854</v>
+        <v>0.1089794486761093</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.006475203670561314</v>
+        <v>0.06030560284852982</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.009220943786203861</v>
+        <v>0.1404556781053543</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.203136429874576e-06</v>
+        <v>0.2032511532306671</v>
       </c>
       <c r="B7" t="n">
-        <v>1.485084567320882e-06</v>
+        <v>0.7864956855773926</v>
       </c>
       <c r="C7" t="n">
-        <v>2.161369593522977e-06</v>
+        <v>0.1012312099337578</v>
       </c>
       <c r="D7" t="n">
-        <v>7.988708603079431e-06</v>
+        <v>0.08546600490808487</v>
       </c>
       <c r="E7" t="n">
-        <v>1.176618980025523e-06</v>
+        <v>0.0355282798409462</v>
       </c>
       <c r="F7" t="n">
-        <v>1.14293152364553e-06</v>
+        <v>0.7217302322387695</v>
       </c>
       <c r="G7" t="n">
-        <v>3.547047526808456e-07</v>
+        <v>0.05286473035812378</v>
       </c>
       <c r="H7" t="n">
-        <v>1.195015784105635e-06</v>
+        <v>0.1095878183841705</v>
       </c>
       <c r="I7" t="n">
-        <v>4.08138220109322e-07</v>
+        <v>0.06031684577465057</v>
       </c>
       <c r="J7" t="n">
-        <v>3.697243755595991e-06</v>
+        <v>0.08520501106977463</v>
       </c>
       <c r="K7" t="n">
-        <v>1.801245048227429e-06</v>
+        <v>0.9467960596084595</v>
       </c>
       <c r="L7" t="n">
-        <v>2.825455339916516e-06</v>
+        <v>0.1121102645993233</v>
       </c>
       <c r="M7" t="n">
-        <v>4.030779564345721e-06</v>
+        <v>0.1577847748994827</v>
       </c>
       <c r="N7" t="n">
-        <v>8.830302249407396e-07</v>
+        <v>0.228763148188591</v>
       </c>
       <c r="O7" t="n">
-        <v>7.116500455595087e-07</v>
+        <v>0.6569246649742126</v>
       </c>
       <c r="P7" t="n">
-        <v>1.319775947195012e-06</v>
+        <v>0.07562259584665298</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.459509803680703e-06</v>
+        <v>0.03938785195350647</v>
       </c>
       <c r="R7" t="n">
-        <v>8.645472462376347e-07</v>
+        <v>0.006023362278938293</v>
       </c>
       <c r="S7" t="n">
-        <v>5.512383154382405e-07</v>
+        <v>0.09244745969772339</v>
       </c>
       <c r="T7" t="n">
-        <v>6.07942695296515e-07</v>
+        <v>0.07851693779230118</v>
       </c>
       <c r="U7" t="n">
-        <v>4.142206080359756e-07</v>
+        <v>0.1657654345035553</v>
       </c>
       <c r="V7" t="n">
-        <v>1.302855707763229e-07</v>
+        <v>0.04888096824288368</v>
       </c>
       <c r="W7" t="n">
-        <v>1.755578864504059e-07</v>
+        <v>0.1181093454360962</v>
       </c>
       <c r="X7" t="n">
-        <v>2.464661520207301e-06</v>
+        <v>0.1664955615997314</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.854967024428333e-07</v>
+        <v>0.2017310559749603</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.916536901575455e-07</v>
+        <v>0.2129576802253723</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.859185772445926e-06</v>
+        <v>0.01199794933199883</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.235548552358523e-08</v>
+        <v>0.1357900202274323</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.304084306269942e-07</v>
+        <v>0.1708818376064301</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.215743036998902e-07</v>
+        <v>0.09585627913475037</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.464233259364846e-06</v>
+        <v>0.3231222033500671</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.950763817148982e-06</v>
+        <v>0.09425144642591476</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.065064111571701e-06</v>
+        <v>0.1510373950004578</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.360840769848437e-06</v>
+        <v>0.1106291338801384</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.745460053825809e-06</v>
+        <v>0.2858477830886841</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6.424711500585545e-07</v>
+        <v>0.1517082899808884</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.406003656891698e-08</v>
+        <v>0.05995490774512291</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.06515744846547e-06</v>
+        <v>0.1652068346738815</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.047317479991762e-07</v>
+        <v>0.05093370378017426</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.565095201134682e-06</v>
+        <v>0.06526751816272736</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.687207372924604e-06</v>
+        <v>0.05817450955510139</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.565722969753551e-07</v>
+        <v>0.1339888274669647</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.790786303805362e-07</v>
+        <v>0.1504639983177185</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.443560103733034e-07</v>
+        <v>0.148932009935379</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.481423510085733e-06</v>
+        <v>0.08201019465923309</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.588365563520711e-07</v>
+        <v>0.06211255863308907</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.383184553560568e-06</v>
+        <v>0.7369579076766968</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.178631919174222e-06</v>
+        <v>0.1240851283073425</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.419266472017625e-06</v>
+        <v>0.01280061341822147</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.53747048823061e-07</v>
+        <v>0.2480434775352478</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.369798951600387e-06</v>
+        <v>0.4732694923877716</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.051009348884691e-06</v>
+        <v>0.05457286536693573</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.104505483657704e-06</v>
+        <v>0.04942247271537781</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.252111575122399e-07</v>
+        <v>0.009516471065580845</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.949081706698053e-06</v>
+        <v>0.01329433545470238</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.935769660121878e-06</v>
+        <v>0.08910898864269257</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.410699716572708e-07</v>
+        <v>0.1637136489152908</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.367779416090343e-06</v>
+        <v>0.1878965795040131</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.106121544580674e-06</v>
+        <v>0.09846912324428558</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.15415070670133e-06</v>
+        <v>0.1228687912225723</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.357205511951179e-07</v>
+        <v>0.1258420497179031</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.950950718310196e-06</v>
+        <v>0.1458215564489365</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.627601235071779e-07</v>
+        <v>0.09283077716827393</v>
       </c>
       <c r="BL7" t="n">
-        <v>7.699850357312243e-07</v>
+        <v>0.08335787057876587</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.628773844686293e-07</v>
+        <v>0.06503716856241226</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.126396341533109e-06</v>
+        <v>0.02809404209256172</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.607515287105343e-06</v>
+        <v>0.01612563803792</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.722224280660157e-06</v>
+        <v>0.1372305452823639</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.250736651556508e-08</v>
+        <v>0.08630899339914322</v>
       </c>
       <c r="BR7" t="n">
-        <v>3.882271926158865e-07</v>
+        <v>0.1270418167114258</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.251700950888335e-06</v>
+        <v>0.05859451368451118</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.813020144771144e-07</v>
+        <v>0.07791822403669357</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.031114718192839e-06</v>
+        <v>0.04603390395641327</v>
       </c>
       <c r="BV7" t="n">
-        <v>1.494343422336897e-07</v>
+        <v>0.3612922430038452</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.224907236974104e-06</v>
+        <v>0.1637592762708664</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.576972408656729e-06</v>
+        <v>0.03063179552555084</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.718809244266595e-06</v>
+        <v>0.07419596612453461</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.988895400652837e-07</v>
+        <v>0.3787543475627899</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.772169859279529e-07</v>
+        <v>0.2523845732212067</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.860231908627611e-07</v>
+        <v>0.08871708810329437</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.87316674732574e-07</v>
+        <v>0.06082436442375183</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.978002899249987e-07</v>
+        <v>0.02185255289077759</v>
       </c>
       <c r="CE7" t="n">
-        <v>2.619180463625526e-07</v>
+        <v>0.2825610041618347</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.257577366686746e-07</v>
+        <v>0.0007421905174851418</v>
       </c>
       <c r="CG7" t="n">
-        <v>1.944395080499817e-06</v>
+        <v>0.02877509035170078</v>
       </c>
       <c r="CH7" t="n">
-        <v>4.778890883017084e-08</v>
+        <v>0.02616778947412968</v>
       </c>
       <c r="CI7" t="n">
-        <v>4.780308131557831e-07</v>
+        <v>0.1905244886875153</v>
       </c>
       <c r="CJ7" t="n">
-        <v>4.272037585906219e-07</v>
+        <v>0.03114949725568295</v>
       </c>
       <c r="CK7" t="n">
-        <v>5.846119393027038e-07</v>
+        <v>0.007829885929822922</v>
       </c>
       <c r="CL7" t="n">
-        <v>4.212579085560719e-07</v>
+        <v>0.0004297024570405483</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.342777977697551e-06</v>
+        <v>0.1960836052894592</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.35009508994699e-06</v>
+        <v>0.4832393825054169</v>
       </c>
       <c r="CO7" t="n">
-        <v>5.448032993626839e-07</v>
+        <v>0.2689419090747833</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.733137762334081e-06</v>
+        <v>0.2171642780303955</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.829629011102952e-07</v>
+        <v>0.02467083930969238</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.233260604749375e-06</v>
+        <v>0.2187367975711823</v>
       </c>
       <c r="CS7" t="n">
-        <v>1.191664978250628e-06</v>
+        <v>0.04770924896001816</v>
       </c>
       <c r="CT7" t="n">
-        <v>1.054534436661925e-06</v>
+        <v>0.1517931222915649</v>
       </c>
       <c r="CU7" t="n">
-        <v>8.100399213617493e-07</v>
+        <v>0.07010272890329361</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.168938979390077e-06</v>
+        <v>0.005489279981702566</v>
       </c>
       <c r="CW7" t="n">
-        <v>5.156909992365399e-07</v>
+        <v>0.2642819881439209</v>
       </c>
       <c r="CX7" t="n">
-        <v>3.709108398197714e-07</v>
+        <v>0.02218220941722393</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.734323063828924e-06</v>
+        <v>0.03386971727013588</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.689204615715425e-07</v>
+        <v>0.004141725599765778</v>
       </c>
       <c r="DA7" t="n">
-        <v>9.211755980231828e-08</v>
+        <v>0.1770937740802765</v>
       </c>
       <c r="DB7" t="n">
-        <v>9.070241162589809e-07</v>
+        <v>0.004600335378199816</v>
       </c>
       <c r="DC7" t="n">
-        <v>7.064621740937582e-07</v>
+        <v>0.01445305161178112</v>
       </c>
       <c r="DD7" t="n">
-        <v>7.680120717168393e-08</v>
+        <v>0.0117040853947401</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.246574356628116e-06</v>
+        <v>0.2560743093490601</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.911991714427131e-06</v>
+        <v>0.09139058738946915</v>
       </c>
       <c r="DG7" t="n">
-        <v>8.572606020607054e-07</v>
+        <v>0.1170818358659744</v>
       </c>
       <c r="DH7" t="n">
-        <v>6.017061195962015e-07</v>
+        <v>0.1230356097221375</v>
       </c>
       <c r="DI7" t="n">
-        <v>3.080691840295913e-06</v>
+        <v>0.1557507812976837</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.419392560819688e-06</v>
+        <v>0.3351753056049347</v>
       </c>
       <c r="DK7" t="n">
-        <v>1.314948008257488e-06</v>
+        <v>0.1181115582585335</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.813347353163408e-06</v>
+        <v>0.09695075452327728</v>
       </c>
       <c r="DM7" t="n">
-        <v>8.996250926429639e-07</v>
+        <v>0.1729710102081299</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.115408963414666e-06</v>
+        <v>0.007911350578069687</v>
       </c>
       <c r="DO7" t="n">
-        <v>9.702790748633561e-07</v>
+        <v>0.1313591301441193</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.201356553792721e-06</v>
+        <v>0.05539925768971443</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1.930876123878988e-06</v>
+        <v>0.09526272863149643</v>
       </c>
       <c r="DR7" t="n">
-        <v>1.579798322381976e-06</v>
+        <v>0.0008581876754760742</v>
       </c>
       <c r="DS7" t="n">
-        <v>1.727545736684988e-06</v>
+        <v>0.01917712390422821</v>
       </c>
       <c r="DT7" t="n">
-        <v>1.347453689959366e-06</v>
+        <v>0.0341733805835247</v>
       </c>
       <c r="DU7" t="n">
-        <v>1.602100780928595e-07</v>
+        <v>0.08748755604028702</v>
       </c>
       <c r="DV7" t="n">
-        <v>4.485317219860008e-07</v>
+        <v>0.02545995265245438</v>
       </c>
       <c r="DW7" t="n">
-        <v>6.777505632271641e-07</v>
+        <v>0.02634235844016075</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.412540541423368e-06</v>
+        <v>0.1565201729536057</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.682019387772016e-06</v>
+        <v>0.02534237504005432</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.635042382185929e-08</v>
+        <v>0.009736385196447372</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.54574718180811e-06</v>
+        <v>0.05760834366083145</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.505853674643731e-06</v>
+        <v>0.01628877967596054</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.162752252843347e-06</v>
+        <v>0.01576653681695461</v>
       </c>
       <c r="ED7" t="n">
-        <v>4.54616923661888e-07</v>
+        <v>0.1482990086078644</v>
       </c>
       <c r="EE7" t="n">
-        <v>2.221450472461584e-07</v>
+        <v>0.2137060761451721</v>
       </c>
       <c r="EF7" t="n">
-        <v>8.041263868108217e-07</v>
+        <v>0.0465109571814537</v>
       </c>
       <c r="EG7" t="n">
-        <v>4.702943954271177e-07</v>
+        <v>0.1159247308969498</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.387386134865665e-07</v>
+        <v>0.08798132091760635</v>
       </c>
       <c r="EI7" t="n">
-        <v>4.187142621958628e-06</v>
+        <v>0.02929581888020039</v>
       </c>
       <c r="EJ7" t="n">
-        <v>4.207871882044856e-07</v>
+        <v>0.01708107814192772</v>
       </c>
       <c r="EK7" t="n">
-        <v>5.644954512717959e-07</v>
+        <v>0.1513175666332245</v>
       </c>
       <c r="EL7" t="n">
-        <v>1.35042938609331e-07</v>
+        <v>0.03737261146306992</v>
       </c>
       <c r="EM7" t="n">
-        <v>7.848382779229723e-07</v>
+        <v>0.04409877210855484</v>
       </c>
       <c r="EN7" t="n">
-        <v>3.855236840877296e-08</v>
+        <v>0.01463219709694386</v>
       </c>
       <c r="EO7" t="n">
-        <v>1.860011821008811e-06</v>
+        <v>0.03591924905776978</v>
       </c>
       <c r="EP7" t="n">
-        <v>1.660268367231765e-06</v>
+        <v>0.1692292839288712</v>
       </c>
       <c r="EQ7" t="n">
-        <v>1.256781956726627e-06</v>
+        <v>0.1045800372958183</v>
       </c>
       <c r="ER7" t="n">
-        <v>2.88281989924144e-06</v>
+        <v>0.05895515903830528</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.050020955517539e-06</v>
+        <v>0.1439808756113052</v>
       </c>
       <c r="ET7" t="n">
-        <v>1.948021917996812e-06</v>
+        <v>0.1361131221055984</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.271253495360725e-06</v>
+        <v>0.002081374637782574</v>
       </c>
       <c r="EV7" t="n">
-        <v>8.492189635944669e-07</v>
+        <v>0.04477068036794662</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.854843617365987e-06</v>
+        <v>0.01598858274519444</v>
       </c>
       <c r="EX7" t="n">
-        <v>9.050559697243443e-07</v>
+        <v>0.01118328329175711</v>
       </c>
       <c r="EY7" t="n">
-        <v>6.423728677873441e-07</v>
+        <v>0.2843316197395325</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.736136425734003e-07</v>
+        <v>0.02783290296792984</v>
       </c>
       <c r="FA7" t="n">
-        <v>2.269862307002768e-06</v>
+        <v>0.01940989680588245</v>
       </c>
       <c r="FB7" t="n">
-        <v>3.161387382988323e-07</v>
+        <v>0.06085424497723579</v>
       </c>
       <c r="FC7" t="n">
-        <v>5.08569200974307e-07</v>
+        <v>0.1861918568611145</v>
       </c>
       <c r="FD7" t="n">
-        <v>2.684740820768639e-07</v>
+        <v>0.03779705613851547</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.589155402825781e-07</v>
+        <v>0.02186604216694832</v>
       </c>
       <c r="FF7" t="n">
-        <v>2.11309114206415e-07</v>
+        <v>0.04267516732215881</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.246122792508686e-06</v>
+        <v>0.05986714735627174</v>
       </c>
       <c r="FH7" t="n">
-        <v>7.526008971581177e-07</v>
+        <v>0.1145360320806503</v>
       </c>
       <c r="FI7" t="n">
-        <v>8.345558057953895e-07</v>
+        <v>0.06178056821227074</v>
       </c>
       <c r="FJ7" t="n">
-        <v>9.066155826076283e-07</v>
+        <v>0.09101630002260208</v>
       </c>
       <c r="FK7" t="n">
-        <v>1.046369675350434e-06</v>
+        <v>0.0288570411503315</v>
       </c>
       <c r="FL7" t="n">
-        <v>1.922343926707981e-06</v>
+        <v>0.2189690172672272</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.169104621112638e-06</v>
+        <v>0.1348101496696472</v>
       </c>
       <c r="FN7" t="n">
-        <v>5.405415777204325e-07</v>
+        <v>0.07729102671146393</v>
       </c>
       <c r="FO7" t="n">
-        <v>1.290018531108217e-06</v>
+        <v>0.1267860233783722</v>
       </c>
       <c r="FP7" t="n">
-        <v>2.345339567000337e-07</v>
+        <v>0.1824933290481567</v>
       </c>
       <c r="FQ7" t="n">
-        <v>1.739844947223901e-06</v>
+        <v>0.006786460056900978</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.135190359491389e-06</v>
+        <v>0.07214483618736267</v>
       </c>
       <c r="FS7" t="n">
-        <v>8.677519645061693e-07</v>
+        <v>0.08656161278486252</v>
       </c>
       <c r="FT7" t="n">
-        <v>5.265557661005005e-07</v>
+        <v>0.0307519119232893</v>
       </c>
       <c r="FU7" t="n">
-        <v>6.969513322019338e-08</v>
+        <v>0.1237631514668465</v>
       </c>
       <c r="FV7" t="n">
-        <v>4.576343144435668e-07</v>
+        <v>0.02631955966353416</v>
       </c>
       <c r="FW7" t="n">
-        <v>1.44899257037423e-08</v>
+        <v>0.03545481711626053</v>
       </c>
       <c r="FX7" t="n">
-        <v>1.352660774500691e-06</v>
+        <v>0.005438901484012604</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.337899902864592e-06</v>
+        <v>0.1513565480709076</v>
       </c>
       <c r="FZ7" t="n">
-        <v>1.144486532211886e-06</v>
+        <v>0.07433918863534927</v>
       </c>
       <c r="GA7" t="n">
-        <v>5.272428325042711e-07</v>
+        <v>0.05640976130962372</v>
       </c>
       <c r="GB7" t="n">
-        <v>2.916415269282879e-06</v>
+        <v>0.02550790458917618</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.186745976156089e-06</v>
+        <v>0.2440452873706818</v>
       </c>
       <c r="GD7" t="n">
-        <v>4.722081428099045e-07</v>
+        <v>0.1470266282558441</v>
       </c>
       <c r="GE7" t="n">
-        <v>5.069659323453379e-07</v>
+        <v>0.0955212414264679</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.461830265725439e-06</v>
+        <v>0.06363827735185623</v>
       </c>
       <c r="GG7" t="n">
-        <v>5.119376282891608e-07</v>
+        <v>0.06379368901252747</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>0.04821976274251938</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.180053472518921</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.07462581992149353</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.9842991232872009</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.100153386592865</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.05112748220562935</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.289886862039566</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.02137869596481323</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.03537950664758682</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.04403417930006981</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.42412543296814</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.09350790083408356</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.275883436203003</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.118407666683197</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.1437629908323288</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.07281884551048279</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.2203172594308853</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.1075186803936958</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.1374626755714417</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.0443861111998558</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.03032288886606693</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.002601563697680831</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.03006064146757126</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.1635884940624237</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.08594733476638794</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>0.1140008643269539</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>0.219104215502739</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>0.06320894509553909</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.06843673437833786</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>0.09568345546722412</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.001887012273073196</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.2083368450403214</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.3433495461940765</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>0.2477605938911438</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>0.09742795675992966</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.05959497764706612</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>0.167826920747757</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>0.376638263463974</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.02125122025609016</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>0.0708889365196228</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>0.3762805163860321</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>0.09885496646165848</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>0.03787469118833542</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>0.02619418874382973</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>0.0740286186337471</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>0.03078043088316917</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>0.5086351633071899</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>0.03553358465433121</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.2868251204490662</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>0.06575895100831985</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>0.01785608008503914</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.0626409575343132</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>0.09862108528614044</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>0.1531261801719666</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>0.1804287284612656</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>0.2019788324832916</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>0.2057065963745117</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>0.008334524929523468</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>0.1789284646511078</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>0.04694664850831032</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>0.1409294903278351</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>0.07100862264633179</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>0.182880699634552</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>0.0005818679928779602</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>0.2518650889396667</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>0.1303258985280991</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>0.1746102273464203</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>0.02863025292754173</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>0.03175273165106773</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>0.04069478809833527</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>0.07489499449729919</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>0.01281829550862312</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>0.05923611670732498</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>0.4478862285614014</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>0.03432229533791542</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>0.3604465425014496</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>0.1669772267341614</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>0.07198771834373474</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>0.0341663584113121</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>0.06293296813964844</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>0.1965661942958832</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>0.003450034186244011</v>
       </c>
       <c r="CE8" t="n">
-        <v>0</v>
+        <v>0.4201636910438538</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>0.0006149895489215851</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>0.3526966869831085</v>
       </c>
       <c r="CH8" t="n">
-        <v>0</v>
+        <v>0.08043316006660461</v>
       </c>
       <c r="CI8" t="n">
-        <v>0</v>
+        <v>0.03638859465718269</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>0.03501419350504875</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>0.03053084760904312</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>0.03078805655241013</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>0.1810021549463272</v>
       </c>
       <c r="CN8" t="n">
-        <v>0</v>
+        <v>0.3779767155647278</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>0.3255605101585388</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>0.3862558603286743</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0</v>
+        <v>0.2674976885318756</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>0.1214997246861458</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>0.2039812356233597</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>0.03952746465802193</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>0.1349974572658539</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>0.0131483618170023</v>
       </c>
       <c r="CW8" t="n">
-        <v>0</v>
+        <v>0.3970142006874084</v>
       </c>
       <c r="CX8" t="n">
-        <v>0</v>
+        <v>0.02660354599356651</v>
       </c>
       <c r="CY8" t="n">
-        <v>0</v>
+        <v>0.3264201581478119</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>0.03440259024500847</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>0.03539171814918518</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>0.04275473207235336</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>0.01022843085229397</v>
       </c>
       <c r="DD8" t="n">
-        <v>0</v>
+        <v>0.06550609320402145</v>
       </c>
       <c r="DE8" t="n">
-        <v>0</v>
+        <v>0.06624549627304077</v>
       </c>
       <c r="DF8" t="n">
-        <v>0</v>
+        <v>0.01462402939796448</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>0.2734626233577728</v>
       </c>
       <c r="DH8" t="n">
-        <v>0</v>
+        <v>0.09983512759208679</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>0.216727077960968</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>0.3460796773433685</v>
       </c>
       <c r="DK8" t="n">
-        <v>0</v>
+        <v>0.02409379184246063</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>0.4222858846187592</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>0.0007037222385406494</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>0.02259443327784538</v>
       </c>
       <c r="DO8" t="n">
-        <v>0</v>
+        <v>0.2248353362083435</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>0.03304349631071091</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>0.2175433933734894</v>
       </c>
       <c r="DR8" t="n">
-        <v>0</v>
+        <v>0.004493359476327896</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>0.005623821169137955</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>0.1268526017665863</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>0.09641312062740326</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>0.3700858950614929</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>0.0375484898686409</v>
       </c>
       <c r="DX8" t="n">
-        <v>0</v>
+        <v>0.2960830926895142</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>0.03776226937770844</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>0.233150839805603</v>
       </c>
       <c r="EA8" t="n">
-        <v>0</v>
+        <v>0.07949042320251465</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>0.2741952836513519</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>0.1050923466682434</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>0.5293577313423157</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>0.3173667788505554</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>0.07443085312843323</v>
       </c>
       <c r="EG8" t="n">
-        <v>0</v>
+        <v>0.2733608484268188</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>0.1410391330718994</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>0.3470999002456665</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0</v>
+        <v>0.0086098313331604</v>
       </c>
       <c r="EK8" t="n">
-        <v>0</v>
+        <v>0.05420217290520668</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>0.02691536769270897</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>0.02127822861075401</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>0.03218026459217072</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>0.125061959028244</v>
       </c>
       <c r="EP8" t="n">
-        <v>0</v>
+        <v>0.4113290011882782</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>0.07797709852457047</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>0.2461560368537903</v>
       </c>
       <c r="ES8" t="n">
-        <v>0</v>
+        <v>0.1619510352611542</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>0.1821494847536087</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>0.1563740372657776</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>0.1326412111520767</v>
       </c>
       <c r="EW8" t="n">
-        <v>0</v>
+        <v>0.1761903613805771</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>0.006344618275761604</v>
       </c>
       <c r="EY8" t="n">
-        <v>0</v>
+        <v>0.4217487275600433</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>0.02117528393864632</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>0.393611878156662</v>
       </c>
       <c r="FB8" t="n">
-        <v>0</v>
+        <v>0.06398166716098785</v>
       </c>
       <c r="FC8" t="n">
-        <v>0</v>
+        <v>0.06720744073390961</v>
       </c>
       <c r="FD8" t="n">
-        <v>0</v>
+        <v>0.003004001453518867</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>0.03348497301340103</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>0.04610896483063698</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>0.07889056205749512</v>
       </c>
       <c r="FH8" t="n">
-        <v>0</v>
+        <v>0.1187369525432587</v>
       </c>
       <c r="FI8" t="n">
-        <v>0</v>
+        <v>0.2136484831571579</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0</v>
+        <v>0.002245388925075531</v>
       </c>
       <c r="FK8" t="n">
-        <v>0</v>
+        <v>0.4578084945678711</v>
       </c>
       <c r="FL8" t="n">
-        <v>0</v>
+        <v>0.0207013227045536</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>0.08846188336610794</v>
       </c>
       <c r="FN8" t="n">
-        <v>0</v>
+        <v>0.3539554178714752</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>0.2403749078512192</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>0.07677143812179565</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0</v>
+        <v>0.05183927714824677</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>0.05147701129317284</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>0.242207944393158</v>
       </c>
       <c r="FT8" t="n">
-        <v>0</v>
+        <v>0.3511030375957489</v>
       </c>
       <c r="FU8" t="n">
-        <v>0</v>
+        <v>0.1790815442800522</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>0.0695682168006897</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>0.0999448299407959</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>0.3260941207408905</v>
       </c>
       <c r="FY8" t="n">
-        <v>0</v>
+        <v>0.05913982167840004</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0</v>
+        <v>0.2839395403862</v>
       </c>
       <c r="GA8" t="n">
-        <v>0</v>
+        <v>0.1505799889564514</v>
       </c>
       <c r="GB8" t="n">
-        <v>0</v>
+        <v>0.4654358923435211</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>0.07583939284086227</v>
       </c>
       <c r="GD8" t="n">
-        <v>0</v>
+        <v>0.1185587495565414</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>0.425289660692215</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>0.07093250006437302</v>
       </c>
       <c r="GG8" t="n">
+        <v>0.02244162932038307</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.0002260903711430728</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002061613136902452</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0005432320758700371</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0008149017230607569</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0005768066039308906</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0008422377286478877</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0003628674312494695</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.000234164486755617</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0002196162677137181</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.481562503613532e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002577414968982339</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0006690038135275245</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.001276141032576561</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001017464441247284</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0004099544312339276</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.479442628100514e-05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0004672252107411623</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0001390794204780832</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.676489955571014e-05</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8.641483873361722e-05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5.612143286271021e-05</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0002292829158250242</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.0002947926113847643</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0003223356616217643</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0002798377827275544</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7.305190956685692e-05</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.0002323176304344088</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0002032957563642412</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.0003385819727554917</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.0002178051800001413</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.0004079954524058849</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0002236172294942662</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0004916466423310339</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>6.24466993031092e-05</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0004291364457458258</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>3.269950684625655e-05</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>4.806300421478227e-05</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0005665126373060048</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.0001577310758875683</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.0003212845185771585</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.0002620212035253644</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0002937642275355756</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.685392872896045e-05</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.0001390500692650676</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.403643833938986e-05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.627068559173495e-05</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.002172680571675301</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.295290510635823e-06</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.000335927092237398</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.0006839835550636053</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.00034394531394355</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7.919583731563762e-05</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.0001868977560661733</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.0001668978802626953</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.022454519756138e-05</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0003712866455316544</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.0004487084224820137</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.0001497716002631932</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.658559894072823e-05</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.0002010033495025709</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>7.514340541092679e-05</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0001637496170587838</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.0002032775664702058</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>7.75397420511581e-05</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.0002681568148545921</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>9.329093154519796e-05</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.0001615023356862366</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0004987774882465601</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.0002775032771751285</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.0003534584539011121</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>6.535223656101152e-05</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5.885183054488152e-05</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.0001067753546521999</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.001285948557779193</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8.046578295761719e-05</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.0005975823733024299</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0001876013993751258</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.0003283728437963873</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0003560976474545896</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>5.129992496222258e-05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.0001796948054106906</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>8.575155516155064e-05</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.0007206823211163282</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.0001445743255317211</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.0002672692353371531</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.0001362377515761182</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.0001860368502093479</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>3.726278009708039e-06</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>3.034119436051697e-05</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>8.769685518927872e-05</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0002636060526128858</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.001154066063463688</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0003473794786259532</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.000390092987800017</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>6.530826794914901e-05</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.902861549751833e-05</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>7.995856140041724e-05</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>2.814698018482886e-05</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>4.211253690300509e-05</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>4.195358997094445e-06</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.0007028329418972135</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.0001615748042240739</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.0003472385287750512</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.0001142148903454654</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0001815018040360883</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>3.727421062649228e-05</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>1.064802381733898e-05</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.0001503772946307436</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0002103068691212684</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.0002674447023309767</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>5.571214933297597e-05</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.000261595007032156</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.0001241114223375916</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.0006322400295175612</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.0001728795759845525</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.0006600031047128141</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>9.226022666553035e-05</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>6.035828846506774e-06</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.0003917870635632426</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>8.182056626537815e-05</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0001373431587126106</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.0001600897958269343</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0002420306991552934</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.000268777774181217</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.0002558210981078446</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.0004158710653427988</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.000164029115694575</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.00045409458107315</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>6.460513395722955e-05</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>5.315473390510306e-05</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.0005547216860577464</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.0003110375255346298</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>3.471668242127635e-05</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0007753626559861004</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.0005343309021554887</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>7.207503222161904e-05</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.0004077526973560452</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>6.282719550654292e-05</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.0002729934058152139</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.0001062212031683885</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0002029801980825141</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>5.994347156956792e-05</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>1.131865610659588e-05</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>9.068723738892004e-05</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>4.010380507679656e-05</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.0003167059330735356</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.0001472451840527356</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.0002696563024073839</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.0001232065260410309</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.0001460944477003068</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.0001286365004489198</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>5.149368007550947e-05</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.0002367070846958086</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>4.693489245255478e-05</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.000797886517830193</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0.000140116098918952</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.0003197016194462776</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>6.102788393036462e-05</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.0002131230139639229</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>6.198080518515781e-05</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>5.747674367739819e-05</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0.0001875711022876203</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>8.964083826867864e-05</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.0002364748797845095</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.000175509398104623</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.0003967482480220497</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.0001010453852359205</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>8.910105862014461e-06</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0.0001964580733329058</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.0001549784792587161</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.0001707878836896271</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.0003049064252991229</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.0006393889198079705</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>8.253337000496686e-05</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.000104602673673071</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.0001413983991369605</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.0001417199819115922</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>1.167004666058347e-05</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.0001515767071396112</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.0002872870827559382</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.0001349370286334306</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0.0003812643699347973</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>5.936237721471116e-05</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.0001576373178977519</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0.0001984351692954078</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.000255355320405215</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.0004583286354318261</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0.0001221910351887345</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>9.929269435815513e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.001381998183205724</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01027046609669924</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.002210558159276843</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.006638744845986366</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0008391736773774028</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.002615351229906082</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0027171541005373</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00265170494094491</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001249524764716625</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0003381888964213431</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01043603662401438</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.002577041042968631</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.00980096124112606</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002324274275451899</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0004681660793721676</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.002205234253779054</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.0007076694746501744</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.001018337090499699</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0004686460306402296</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.001498321886174381</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.0002531868231017143</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.0006772449123673141</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.0009630001150071621</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.001349432277493179</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.00027685851091519</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.0008707413799129426</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.002011150820180774</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.0006113570416346192</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.788622027263045e-05</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.0009652707958593965</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.002360675483942032</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.0005123003502376378</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.001772454124875367</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.001338226720690727</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>9.068594954442233e-05</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.0008861776441335678</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.0004386483924463391</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.003158129751682281</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.0009240701328963041</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.00184127758257091</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.002655160613358021</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.001634346088394523</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.0003835742827504873</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.847296026535332e-05</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.0002039814862655476</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.0004989945446141064</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.006341726519167423</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.029299816465937e-05</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.002812498481944203</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.003777628997340798</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.0002681570185814053</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.000270921504124999</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.0008884314447641373</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.0006526983343064785</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.0006180834025144577</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.0001454261946491897</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.001667916309088469</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.001090506324544549</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7.424774230457842e-05</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.001806900021620095</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.0003377062967047095</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.001070987549610436</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.001964616123586893</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.0005107494071125984</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.0009966476354748011</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.0004953853785991669</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.0007007948588579893</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>2.568053605500609e-05</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.0001647911703912541</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.0009641501237638295</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9.245061664842069e-05</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.0002987938350997865</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.0008168212370947003</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.005438938736915588</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.0004259155539330095</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.002815148560330272</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.000913209340069443</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.001309101702645421</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.000813961960375309</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.0006155025912448764</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.001505889929831028</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.0003411206125747412</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.003143153619021177</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.0007830706890672445</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.002515309723094106</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.0002458328381180763</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.0004313196695875376</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>4.419176548253745e-05</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.0007708710618317127</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.000383880891604349</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.001457772799767554</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.003717571962624788</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0.001696066465228796</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.005160663276910782</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.001506846398115158</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.0008373754099011421</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0.001550085376948118</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.0003365557640790939</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0.0008829599246382713</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>7.359296432696283e-05</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.003013123292475939</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0.0007314634276553988</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.002540641464293003</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>6.127909000497311e-05</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.0004056188627146184</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.0001674369559623301</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.0007087482372298837</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0.000581279513426125</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.0005532180657610297</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.002326565561816096</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0.0009467685595154762</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.001629960723221302</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.002066151006147265</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.002693187678232789</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0.0003076824941672385</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.003889598650857806</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0.0005390162696130574</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.0003932295367121696</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0.001545913750305772</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0.0009802757995203137</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.001115749473683536</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.000513852050062269</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>2.154100366169587e-05</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.001352685736492276</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0.0005578584386967123</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0.002869451884180307</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0.0001110784069169313</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>8.411094313487411e-05</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0.0009726907592266798</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0.0009503530454821885</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.0003790504124481231</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0.001058999798260629</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0.0003029434883501381</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0.003481905441731215</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0.002826016629114747</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0.0002100639685522765</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.002681309590116143</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0.0006872175727039576</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.002390905283391476</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.000341594364726916</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.000446948892204091</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0.0001965127012226731</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0.0008398272912018001</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0.0002118115226039663</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0.000779957277700305</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.002676325850188732</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>4.660129707190208e-05</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.001729687443003058</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0.0002973839873448014</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.0007649844046682119</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0.001879424322396517</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0.0008864256669767201</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0.001155988546088338</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0.0003341651463415474</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.003535586409270763</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0.0006769282626919448</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.002932408824563026</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>9.967941150534898e-05</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.0005480136023834348</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0.0002910434268414974</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0.0009309909655712545</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0.0006677448400296271</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0.0006620463682338595</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.001779388054274023</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0.0006572555284947157</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.001220540842041373</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.0007780077867209911</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.0007281395373865962</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0.0001036823523463681</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0.0006996858865022659</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0.001579651492647827</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0.0003786379238590598</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.004025270696729422</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0.0009465900366194546</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0.0006394442170858383</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0.001462262938730419</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0.0005423744441941381</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0.0007247126195579767</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0.0002181868767365813</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0.001877176575362682</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.000948397908359766</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.002559542655944824</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>7.547374116256833e-05</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.002124891150742769</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0.002238813554868102</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.0008282228372991085</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0.002132912864908576</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0.001226380933076143</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0.0001404320355504751</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.002710319589823484</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01052618492394686</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0001589418388903141</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0006877303239889443</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.001666528172791004</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.008341564796864986</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.002019336447119713</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.002997686620801687</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.001918939640745521</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.001895571476779878</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.01364295370876789</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0006092279218137264</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.00296306423842907</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001617227448150516</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.008343696594238281</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.420087836682796e-05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.000317815225571394</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.004382176790386438</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.0006441724253818393</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.000988955027423799</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.001327367033809423</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.002271352568641305</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.001554445712827146</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.001293123234063387</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.0005156658589839935</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.00256285211071372</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.119278259575367e-05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.0008333067526109517</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.0002660593600012362</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.001393100013956428</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.0008541755378246307</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.003495882032439113</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.0008047640440054238</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.0006788063328713179</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.004091451875865459</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.0007498105987906456</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>5.328253610059619e-05</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.001456716912798584</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.001767668873071671</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.001639831927604973</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.0005287429667077959</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.001505876542069018</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.001500545651651919</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.003238189965486526</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.0008677829173393548</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.002233519684523344</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.009619509801268578</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.001618777634575963</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.0003223645617254078</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.001577967777848244</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.005019501782953739</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.0003180729108862579</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.0002261748013552278</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.001274854876101017</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.0003492786781862378</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.0008283657371066511</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.0005118081462569535</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.0006680021760985255</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.00122909143101424</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.002052458701655269</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.0005473233759403229</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.00207266490906477</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.0002588187053333968</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.0004760401789098978</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.002501065144315362</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.875487866229378e-05</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.0001692903751973063</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.002398528158664703</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.001551958033815026</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.003354074899107218</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.0001783896586857736</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.002168126869946718</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.0002962903818115592</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.006129694171249866</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.0006221873336471617</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.002453036839142442</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.0006442260928452015</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.002891237847507</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.0007613211637362838</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.0005747812101617455</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.0008045937865972519</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.001455284538678825</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.003027588361874223</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.0005199253209866583</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.0001939312205649912</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.001151864649727941</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.002298459410667419</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.001278295065276325</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.0004359203740023077</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0.0001480589417042211</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.0003171123098582029</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.004738634917885065</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.001332239364273846</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.001368154771625996</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.002917208708822727</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.001679406501352787</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0.000244741328060627</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0.0003114935534540564</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0.0004144740523770452</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0.0007900390774011612</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.002928351517766714</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0.0003477930149529129</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>6.755755748599768e-06</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.001157046412117779</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.002280672313645482</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0.0004852836136706173</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0.0006768038729205728</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0.0002654269919730723</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.0002287063980475068</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.004978636279702187</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.001812233706004918</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.002407400868833065</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.002274581231176853</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.001758545986376703</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0.0003230771108064801</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.001576739479787648</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>2.836761996150017e-05</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.001979165710508823</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.001840334269218147</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0.001103913644328713</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0.00198478065431118</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0.0006643922533839941</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.001428272691555321</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.000369139073882252</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0.002422494813799858</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0.0004564591799862683</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0.002269868738949299</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.001227807719260454</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0.0008511352352797985</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0.001240206765942276</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.001218909164890647</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.002026865258812904</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0.0002872032346203923</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0.001079489011317492</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0.003467518836259842</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0.0009751705219969153</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0.0004282479349058121</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0.001452045049518347</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0.0001485126267652959</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>0.001983308698982</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.001360876252874732</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0.0007346399361267686</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0.0001018983384710737</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0.000380111247068271</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0.001109312637709081</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.001310494961217046</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0.0001702895970083773</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0.0003479419974610209</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.00318818399682641</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.002035695826634765</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0.0004182688717264682</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>6.541586481034756e-05</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0.001044685370288789</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0.001250365166924894</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0.003643779549747705</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0.0003585412341635674</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>8.837931090965867e-05</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.001865044934675097</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.001967781223356724</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0.00115948636084795</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0.0006170279812067747</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>0.000464585842564702</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0.0007118690409697592</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0.0029408298432827</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0.001947101904079318</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0.0006639109924435616</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.0009749395539984107</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.00299278530292213</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0.001271155895665288</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0.003571669338271022</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0.002400423865765333</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>0.0008112137438729405</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.00119917094707489</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0.004488921258598566</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>0.003030752530321479</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.0003525998326949775</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.0006569339893758297</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>5.52787387277931e-05</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0.001819643890485168</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0.001384386094287038</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0.002333402633666992</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.0003510827082209289</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0.00135047291405499</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>2.182316893595271e-05</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>0.00234857783652842</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.002357635414227843</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0.0001075249383575283</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0.001371277961879969</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0.00242637493647635</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1.700505181112533e-09</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.176726437459365e-09</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.315485746531067e-10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.263069370262883e-09</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.859884801724832e-09</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.292186606136283e-09</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.739346332576332e-10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.679416272715173e-09</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.190926940397574e-10</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.776288227617329e-09</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.165891993006653e-09</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.532637350365462e-09</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.107725105560121e-09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9.074563322997165e-11</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.93666307832541e-09</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.370334566987765e-10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.259953779670809e-09</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.260411302579257e-11</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8.073709478750857e-10</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8.040391685781856e-10</v>
+      </c>
+      <c r="U13" t="n">
+        <v>9.037715020809856e-11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.542255377908532e-11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.75432204821513e-10</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.780044889265753e-09</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.09617495636094e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.696279561258507e-09</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.065090096818437e-11</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.717020521549102e-10</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.317007696817086e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.294977791665985e-09</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5.717084028411534e-10</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.256954428376702e-10</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.018886752746084e-09</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.487495375293804e-10</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.521446857388753e-10</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.428540979426685e-10</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>4.409794196469363e-10</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.356135204133579e-09</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>3.263258552266279e-10</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.700030199420667e-10</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>6.884404157858626e-10</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.522340752404318e-10</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7.880323615871987e-10</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.322528891956054e-11</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.866680805714623e-10</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.693740561836137e-10</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.49525422546526e-09</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.498317914183644e-09</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.588153745821444e-10</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.091298106383533e-09</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.268879445959215e-09</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.813496212203617e-11</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.174245256585493e-09</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.324038323424759e-09</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.408425208739629e-10</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.266626746878387e-09</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.723489684302137e-10</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.252969588667497e-09</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6.077929715075925e-09</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>7.146984670747258e-10</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>5.340308195656007e-10</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.810104954813596e-09</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.93567473161238e-09</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>2.385719954922649e-10</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.03245034743793e-09</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.464362103797967e-10</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.012852189954174e-10</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1.206434174783055e-09</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.748376166066379e-10</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>2.576596158654354e-10</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>4.029359068624672e-10</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>3.158256434154794e-10</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.794298291699306e-10</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1.484281031416401e-09</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>4.227364291953251e-10</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>4.473734438459331e-10</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>3.796511993670038e-10</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>2.122069187038278e-09</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>4.58489662902295e-10</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>2.009410554615343e-10</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>5.918778800406699e-10</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>9.113473309341202e-10</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>1.941012628403627e-10</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>2.488192429872527e-10</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>4.015996979411796e-10</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>4.8724707601977e-10</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1.320251796776972e-09</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>6.967570964633296e-11</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>3.45344253194213e-10</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>3.980554774685174e-10</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>3.594563535713746e-11</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>2.709516611076879e-09</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.421039064197771e-09</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>7.265020807167843e-10</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>1.89714244314132e-09</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.187787868062173e-09</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>7.115378286570717e-10</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>1.300182461694277e-10</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.577339481251272e-09</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>8.8590951241585e-10</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>4.459698166314752e-10</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>2.076981087117957e-10</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>4.903065731198808e-10</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.733363882456707e-11</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.484336098478423e-09</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>4.422111010704555e-10</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>4.816412269015302e-10</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>5.86236725830247e-10</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>2.133527798875434e-10</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>3.448932917038405e-09</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>1.036531527276452e-09</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>9.827264557671356e-10</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>7.043788885496838e-10</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>1.444044550602541e-09</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>1.763428181256188e-09</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>1.332873811321633e-09</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>1.274124250549846e-09</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>1.681240702211539e-09</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>8.423942654545158e-10</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>4.858113356043248e-10</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>2.191050674227313e-09</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>1.0902681535363e-10</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>2.190291004122713e-11</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>5.348743115085597e-10</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>5.732146424186624e-10</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>9.075079576703615e-10</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>9.312122184468308e-10</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>1.258435133877356e-09</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>1.570279684059983e-09</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>1.20516974178031e-09</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>2.792437614473897e-09</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>7.914612853987535e-10</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>7.467962914731174e-10</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>1.60077229249822e-09</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>2.043182012467781e-10</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>9.379762522243595e-10</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>1.443793196109766e-09</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>7.899598197802504e-10</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>1.922768833040323e-09</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>1.321773940299309e-10</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>1.570614083235e-09</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>3.850566046570414e-11</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>7.375998700709374e-10</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>4.68912575435354e-10</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>8.587793809411437e-10</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>3.887903610166887e-10</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>1.109297542711829e-09</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>1.116930770095337e-09</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>2.199137261182926e-10</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>5.243797618348367e-10</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>5.980624884216468e-10</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>1.710799057974555e-09</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>6.085019155221971e-10</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>1.18726339870534e-09</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>5.624382626301383e-10</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>2.517938635371308e-10</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>3.013566063359008e-10</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>4.867938274699668e-10</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>1.428169693618031e-09</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>1.538413285651075e-10</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>6.21775131381952e-10</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>2.362579021308875e-10</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>1.453284159680379e-10</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>4.239661399729755e-10</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>2.244272767626398e-09</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>2.07107508920501e-09</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>1.697638363218346e-09</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>8.122558181611339e-10</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>8.95714891147037e-11</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>9.226223673941547e-10</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>1.122301029887751e-09</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>1.420690676212644e-09</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>2.526533648961049e-09</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>3.870209042133865e-09</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>8.225813918905089e-10</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>1.726769949250695e-09</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>1.394207527205538e-09</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>2.099756146733966e-09</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>4.000749731503106e-11</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>6.357571136206275e-10</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>2.83184420357685e-10</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>1.979737485058308e-10</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>1.349861444843725e-09</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>1.921566239460049e-09</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>2.271024701627766e-09</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>2.113427877148411e-09</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>8.599561340805195e-11</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>2.807281629380043e-10</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>1.340351787892935e-11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2.114090236204902e-08</v>
+      </c>
+      <c r="B15" t="n">
+        <v>6.64010002537907e-08</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.330517651609853e-08</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.359718915239227e-08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.771311985976354e-08</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.757092935709807e-08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.353929746095162e-09</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.597558435013525e-08</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.933004423193552e-09</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7.721481232181304e-09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.709146387924193e-08</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.343946903238248e-08</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.973886476491771e-08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.045958862912812e-08</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7.015221115125314e-08</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.708304964154195e-08</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.746144029368679e-08</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.722110950680872e-09</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.667166209060269e-09</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5.310010209313987e-10</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8.695604236663712e-09</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.706471491364937e-09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.365431501199055e-08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.202211041828605e-08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.75483059194903e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8.317049271511223e-09</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>7.724677786313805e-09</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.588053409941949e-09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.03352606473095e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.591235309130525e-09</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.23303908089656e-08</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.008023696793316e-08</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.649176167324185e-08</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.844811053392959e-09</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.602081122267009e-08</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>3.77272213469837e-10</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>7.32120319923979e-09</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.862808218788814e-08</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>9.567740377747214e-09</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>8.238412618766233e-09</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.841368917927412e-09</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.350323586279956e-08</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.104693663795842e-08</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.267271259626114e-09</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.492404309137555e-10</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.128026948573392e-09</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.559242476418149e-08</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.006139432353393e-08</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>6.200792768140673e-09</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.634742735097007e-08</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5.672411518276022e-08</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>7.791574496707199e-09</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.490871870402088e-09</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.625283019279777e-09</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.810321474479906e-09</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.997426999471145e-10</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.07888151745783e-08</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.295903473419457e-08</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.373530977843984e-08</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1.015768624768043e-08</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>9.415408896984445e-09</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1.632552759645023e-08</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>3.688377825383782e-09</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>3.355731248433358e-10</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.574949592964003e-08</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.936523190224307e-09</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.304349016630681e-10</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>2.689139044775857e-08</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.196307053419332e-08</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1.614881561806669e-08</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.127218207663816e-09</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>2.02346903677153e-08</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>6.50604725649373e-09</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>4.143758403074571e-08</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>6.912694860972124e-09</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1.248089631644689e-08</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>8.812869323193695e-10</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>3.443019380711121e-08</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.707242702764233e-08</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>7.680569069634657e-09</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>3.897936196040064e-09</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>4.585485768870967e-09</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>2.279476518651791e-08</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>2.16139683928418e-09</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>2.121729014703533e-09</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>7.049209216347663e-09</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1.536998261997269e-08</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1.264163107528304e-09</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.808503569122877e-09</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>6.149067921512597e-09</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>1.757378420563782e-08</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>3.3736210269808e-08</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>2.056397008232125e-08</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>2.203922599974817e-09</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>1.54288866127672e-08</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>9.173128034944966e-09</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>1.606723420977119e-09</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>3.454507790934258e-09</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>1.104231195370176e-08</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>2.106213869979001e-09</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>1.95763334431831e-08</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>4.109183660006011e-09</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>3.491008371270254e-09</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>8.860838285329464e-09</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>1.787798709074195e-08</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>4.047828294773126e-09</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>5.978108230664247e-09</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>5.363499866462007e-09</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>1.159739237976964e-08</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1.293650431222204e-08</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>5.957701443293217e-09</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>4.778090811896618e-09</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>8.928680017561419e-09</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>1.308478836392624e-08</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>1.870844812401629e-08</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>1.086879208855862e-08</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>1.635768187568942e-09</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>1.043894082286556e-09</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>8.300711229480839e-09</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>3.694136774257117e-09</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>5.838471039965043e-09</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>7.079283825817129e-09</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>2.519751518548219e-09</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>1.203567823182539e-08</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>6.084795334260207e-09</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>1.990296993881202e-08</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>2.972161849967847e-09</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>1.81296755386029e-08</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>1.495621404501435e-08</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>3.824735639312848e-09</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>2.379642261018944e-08</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>3.212969446053648e-09</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>7.274871816065343e-10</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>2.102102847345577e-08</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>1.766224677623995e-08</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>6.20778983773107e-09</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>3.880982646364828e-09</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>7.159157711100761e-09</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>6.045586253833335e-10</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>6.692824516818519e-09</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>6.469524915786451e-09</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>5.571348271615761e-09</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>1.453727804801019e-09</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>6.822646891890827e-10</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>5.843222350421229e-09</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>1.290273310416978e-08</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>3.1994282778669e-09</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>2.581138858204213e-09</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>1.121509818347022e-08</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>1.694232665272466e-08</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>6.352982140356289e-09</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>8.022172925947757e-10</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>3.601992037971513e-09</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>4.176188284077398e-09</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>2.417154121303611e-08</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>1.920711145686482e-09</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>2.026024015222561e-09</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>3.309310159238521e-09</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>1.348158651381937e-08</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>8.338004731101023e-10</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>4.8608839176012e-10</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>1.490580436858124e-10</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>1.45782874660938e-09</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>5.912766720683749e-09</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>1.139215832779428e-08</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>9.968539771421092e-09</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>9.437279402391141e-09</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>2.38186839141008e-08</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>5.931627633515291e-09</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>6.277022457368275e-09</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>3.741842746762813e-08</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>1.67857621136136e-08</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>2.057545067657429e-08</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>1.309514452429994e-08</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>5.242892342494088e-09</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>9.872214157269354e-09</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>4.525622099293969e-09</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>1.15658309596256e-08</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>1.476281852319516e-08</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>2.582264180261973e-09</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>2.307915858423826e-09</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>1.807179739188314e-09</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>1.342983413366028e-08</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>4.365690919883036e-09</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>2.398715537310636e-08</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>2.608728522091042e-08</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>1.77949157631474e-08</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>2.230323703500403e-09</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>3.216752642032361e-09</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
